--- a/df_list_20260307.xlsx
+++ b/df_list_20260307.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-07 07:08:35</t>
+          <t>2026-03-07 07:57:02</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-07 07:08:35</t>
+          <t>2026-03-07 07:57:02</t>
         </is>
       </c>
     </row>

--- a/df_list_20260307.xlsx
+++ b/df_list_20260307.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-07 07:57:02</t>
+          <t>2026-03-07 08:45:17</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-07 07:57:02</t>
+          <t>2026-03-07 08:45:17</t>
         </is>
       </c>
     </row>

--- a/df_list_20260307.xlsx
+++ b/df_list_20260307.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,6 +448,11 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>키워드</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>수집일</t>
         </is>
       </c>
@@ -478,37 +483,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-07 08:45:17</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A162</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>경상도_문경시</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.gbmg.go.kr/portal/saeol/gosi/list.do?mId=0301060000</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>「문경시 문화예술회관 안전난간 설치사업」신기술・특허공법 선정 기술제안서 제출기한 연장 안내 공고</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46088</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-03-07 08:45:17</t>
+          <t>공법</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-03-07 21:25:54 KST</t>
         </is>
       </c>
     </row>
